--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -15497,7 +15497,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación ISAPRE</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:54</t>
+    <t xml:space="preserve">2026-08-28 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:12</t>
+    <t xml:space="preserve">2026-08-29 05:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:48</t>
+    <t xml:space="preserve">2026-09-07 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2022.xlsx
@@ -2080,7 +2080,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:10</t>
+    <t xml:space="preserve">2026-09-08 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
